--- a/input/old/Metadata _Document SD not posted to FI _ 30 days_200020_000071.xlsx
+++ b/input/old/Metadata _Document SD not posted to FI _ 30 days_200020_000071.xlsx
@@ -422,7 +422,7 @@
         <v>Created on</v>
       </c>
       <c r="B6" t="str">
-        <v>14.01.2026 at 15:50 by ILIYAR</v>
+        <v>14.01.2026 at 15:50 by REDACTED</v>
       </c>
     </row>
     <row r="7">
@@ -430,7 +430,7 @@
         <v>Updated on</v>
       </c>
       <c r="B7" t="str">
-        <v>16.01.2026 at 17:02 by ILIYAR</v>
+        <v>16.01.2026 at 17:02 by REDACTED</v>
       </c>
     </row>
     <row r="8">
